--- a/tests/fixtures/test-pt-data-v0.0.1.xlsx
+++ b/tests/fixtures/test-pt-data-v0.0.1.xlsx
@@ -20,7 +20,8 @@
     <sheet name="mayo_findings" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="henry_ford_findings" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="guardant360_findings" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="tumor_biomarkers" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="foundation_findings" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="tumor_biomarkers" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +50,10 @@
       <i val="1"/>
       <color rgb="00AAAAAA"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="6">
@@ -91,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -107,6 +112,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1127,6 +1133,319 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:W3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>pt_uuid</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>report_uuid</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>accession_no</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>gene</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>nucleotide</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>variant_type</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>result_summary</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>raw_section</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>raw_biomarker</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>raw_method</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>raw_analyte</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>raw_result</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>raw_benefit</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>raw_therapy_assoc</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>raw_biomarker_level</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>raw_variant_interpretation</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>raw_protein_alteration</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>raw_exon</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t>raw_dna_alteration</t>
+        </is>
+      </c>
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t>raw_frequency_pct</t>
+        </is>
+      </c>
+      <c r="V1" s="7" t="inlineStr">
+        <is>
+          <t>raw_genotype</t>
+        </is>
+      </c>
+      <c r="W1" s="7" t="inlineStr">
+        <is>
+          <t>raw_hla_class</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FMI-000001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>EGFR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>p.L858R</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>c.2573T&gt;G</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>mutation</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>detected</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Genomic Findings</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>EGFR L858R</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>NGS</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>DNA</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Detected</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>osimertinib</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Known short variant</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>L858R</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>21</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2573T&gt;G</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FMI-000002</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HLA-A</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>genotype</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>HLA-A*02:01</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Biomarkers</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>HLA-A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>NGS</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>DNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>A*02:01</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>A*02:01</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Class I</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
